--- a/CO国試data/CO_questions_2021.xlsx
+++ b/CO国試data/CO_questions_2021.xlsx
@@ -542,15 +542,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -599,7 +599,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>False</t>
@@ -635,15 +634,15 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -692,7 +691,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>False</t>
@@ -728,15 +726,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -785,7 +783,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>False</t>
@@ -824,12 +821,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -878,7 +875,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>False</t>
@@ -917,12 +913,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>公衆衛生学</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -971,7 +967,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>False</t>
@@ -1007,15 +1002,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1064,7 +1059,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>False</t>
@@ -1100,15 +1094,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>脳・神経</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1157,7 +1151,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>False</t>
@@ -1196,12 +1189,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1250,7 +1243,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>False</t>
@@ -1286,15 +1278,15 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>内分泌</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -1343,7 +1335,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>False</t>
@@ -1379,15 +1370,15 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1436,7 +1427,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>False</t>
@@ -1472,15 +1462,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -1529,7 +1519,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>False</t>
@@ -1565,15 +1554,15 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -1622,7 +1611,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>False</t>
@@ -1658,15 +1646,15 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1715,7 +1703,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>False</t>
@@ -1751,15 +1738,15 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1</v>
       </c>
@@ -1808,7 +1795,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>False</t>
@@ -1844,15 +1830,15 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>4</v>
       </c>
@@ -1901,7 +1887,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>False</t>
@@ -1937,15 +1922,15 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -1994,7 +1979,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>False</t>
@@ -2030,15 +2014,15 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>1</v>
       </c>
@@ -2087,7 +2071,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>False</t>
@@ -2123,15 +2106,15 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>4</v>
       </c>
@@ -2221,15 +2204,15 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2319,15 +2302,15 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>3</v>
       </c>
@@ -2417,15 +2400,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -2474,7 +2457,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>False</t>
@@ -2510,15 +2492,15 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -2567,7 +2549,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>False</t>
@@ -2603,15 +2584,15 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>3</v>
       </c>
@@ -2660,7 +2641,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>True</t>
@@ -2696,15 +2676,15 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
         <v>4</v>
       </c>
@@ -2794,15 +2774,15 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2851,7 +2831,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>False</t>
@@ -2887,15 +2866,15 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>3</v>
       </c>
@@ -2944,7 +2923,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>False</t>
@@ -2980,15 +2958,15 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -3037,7 +3015,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>True</t>
@@ -3073,15 +3050,15 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>4</v>
       </c>
@@ -3130,7 +3107,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>True</t>
@@ -3166,15 +3142,15 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -3223,7 +3199,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>False</t>
@@ -3259,15 +3234,15 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -3316,7 +3291,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>False</t>
@@ -3352,15 +3326,15 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>視能矯正の枠組み</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -3409,7 +3383,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr">
         <is>
           <t>False</t>
@@ -3445,15 +3418,15 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>4</v>
       </c>
@@ -3503,7 +3476,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
       <c r="S33" t="inlineStr">
         <is>
           <t>False</t>
@@ -3539,15 +3511,15 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3596,7 +3568,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
       <c r="S34" t="inlineStr">
         <is>
           <t>False</t>
@@ -3632,15 +3603,15 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>3</v>
       </c>
@@ -3730,15 +3701,15 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3787,7 +3758,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
           <t>False</t>
@@ -3823,15 +3793,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3880,7 +3850,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
           <t>False</t>
@@ -3916,15 +3885,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3973,7 +3942,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
       <c r="S38" t="inlineStr">
         <is>
           <t>True</t>
@@ -4009,15 +3977,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4066,7 +4034,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
           <t>False</t>
@@ -4102,15 +4069,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -4159,7 +4126,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
           <t>False</t>
@@ -4195,15 +4161,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>4</v>
       </c>
@@ -4253,7 +4219,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
           <t>False</t>
@@ -4289,15 +4254,15 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
         <v>1</v>
       </c>
@@ -4346,7 +4311,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
           <t>False</t>
@@ -4382,15 +4346,15 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>3</v>
       </c>
@@ -4480,15 +4444,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -4537,7 +4501,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
           <t>False</t>
@@ -4573,15 +4536,15 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>3</v>
       </c>
@@ -4630,7 +4593,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
           <t>False</t>
@@ -4666,15 +4628,15 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4723,7 +4685,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
           <t>False</t>
@@ -4759,15 +4720,15 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4816,7 +4777,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
       <c r="S47" t="inlineStr">
         <is>
           <t>False</t>
@@ -4852,15 +4812,15 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>2</v>
       </c>
@@ -4909,7 +4869,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr">
         <is>
           <t>False</t>
@@ -4945,15 +4904,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -5002,7 +4961,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr">
         <is>
           <t>False</t>
@@ -5038,15 +4996,15 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
         <v>2</v>
       </c>
@@ -5095,7 +5053,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
       <c r="S50" t="inlineStr">
         <is>
           <t>False</t>
@@ -5131,15 +5088,15 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
         <v>2</v>
       </c>
@@ -5188,7 +5145,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
       <c r="S51" t="inlineStr">
         <is>
           <t>False</t>
@@ -5224,15 +5180,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5281,7 +5237,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
       <c r="S52" t="inlineStr">
         <is>
           <t>False</t>
@@ -5317,15 +5272,15 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5374,7 +5329,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
       <c r="S53" t="inlineStr">
         <is>
           <t>False</t>
@@ -5410,15 +5364,15 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
         <v>3</v>
       </c>
@@ -5467,7 +5421,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
       <c r="S54" t="inlineStr">
         <is>
           <t>False</t>
@@ -5503,15 +5456,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5560,7 +5513,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
       <c r="S55" t="inlineStr">
         <is>
           <t>False</t>
@@ -5596,15 +5548,15 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
         <v>3</v>
       </c>
@@ -5653,7 +5605,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
       <c r="S56" t="inlineStr">
         <is>
           <t>False</t>
@@ -5689,15 +5640,15 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
         <v>4</v>
       </c>
@@ -5746,7 +5697,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
       <c r="S57" t="inlineStr">
         <is>
           <t>True</t>
@@ -5782,15 +5732,15 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -5839,7 +5789,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
       <c r="S58" t="inlineStr">
         <is>
           <t>False</t>
@@ -5875,15 +5824,15 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5932,7 +5881,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
       <c r="S59" t="inlineStr">
         <is>
           <t>False</t>
@@ -5968,15 +5916,15 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
         <v>2</v>
       </c>
@@ -6025,7 +5973,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
       <c r="S60" t="inlineStr">
         <is>
           <t>False</t>
@@ -6061,15 +6008,15 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6118,7 +6065,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
       <c r="S61" t="inlineStr">
         <is>
           <t>False</t>
@@ -6154,15 +6100,15 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ロービジョン</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6211,7 +6157,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
       <c r="S62" t="inlineStr">
         <is>
           <t>False</t>
@@ -6247,15 +6192,15 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>4</v>
       </c>
@@ -6304,7 +6249,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
           <t>True</t>
@@ -6340,15 +6284,15 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
         <v>2</v>
       </c>
@@ -6397,7 +6341,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
           <t>False</t>
@@ -6433,15 +6376,15 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
         <v>3</v>
       </c>
@@ -6490,7 +6433,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
           <t>False</t>
@@ -6526,15 +6468,15 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6583,7 +6525,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
           <t>False</t>
@@ -6619,15 +6560,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>4</v>
       </c>
@@ -6717,15 +6658,15 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
         <v>3</v>
       </c>
@@ -6775,7 +6716,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
           <t>False</t>
@@ -6811,15 +6751,15 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>4</v>
       </c>
@@ -6909,15 +6849,15 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
         <v>4</v>
       </c>
@@ -6967,7 +6907,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
           <t>False</t>
@@ -7003,15 +6942,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>4</v>
       </c>
@@ -7101,15 +7040,15 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>3</v>
       </c>
@@ -7199,15 +7138,15 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7297,15 +7236,15 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>3</v>
       </c>
@@ -7395,15 +7334,15 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -7454,7 +7393,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr">
         <is>
           <t>False</t>
@@ -7490,15 +7428,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7548,7 +7486,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
       <c r="S76" t="inlineStr">
         <is>
           <t>False</t>
@@ -7587,12 +7524,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7641,7 +7578,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
       <c r="S77" t="inlineStr">
         <is>
           <t>False</t>
@@ -7677,15 +7613,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7734,7 +7670,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R78" t="inlineStr"/>
       <c r="S78" t="inlineStr">
         <is>
           <t>False</t>
@@ -7770,15 +7705,15 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達・加齢</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>遺伝</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7827,7 +7762,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr"/>
       <c r="S79" t="inlineStr">
         <is>
           <t>False</t>
@@ -7863,15 +7797,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>眼科薬理学</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>眼薬理学</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7920,7 +7854,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr">
         <is>
           <t>False</t>
@@ -7959,12 +7892,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>健康、疾病、障害の概念</t>
         </is>
       </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -8013,7 +7946,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr">
         <is>
           <t>False</t>
@@ -8049,15 +7981,15 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8106,7 +8038,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr">
         <is>
           <t>False</t>
@@ -8142,15 +8073,15 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>3</v>
       </c>
@@ -8199,7 +8130,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr"/>
       <c r="S83" t="inlineStr">
         <is>
           <t>False</t>
@@ -8235,15 +8165,15 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+          <t>人体の構造と機能及び心身の発達</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>遺伝</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
         <v>3</v>
       </c>
@@ -8292,7 +8222,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R84" t="inlineStr"/>
       <c r="S84" t="inlineStr">
         <is>
           <t>True</t>
@@ -8328,15 +8257,15 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8385,7 +8314,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr"/>
       <c r="S85" t="inlineStr">
         <is>
           <t>False</t>
@@ -8424,12 +8352,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>1</v>
       </c>
@@ -8478,7 +8406,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr"/>
       <c r="S86" t="inlineStr">
         <is>
           <t>False</t>
@@ -8514,15 +8441,15 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>3</v>
       </c>
@@ -8612,15 +8539,15 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>3</v>
       </c>
@@ -8669,7 +8596,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>True</t>
@@ -8705,15 +8631,15 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
         <v>3</v>
       </c>
@@ -8762,7 +8688,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>False</t>
@@ -8798,15 +8723,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8855,7 +8780,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>False</t>
@@ -8891,15 +8815,15 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
         <v>3</v>
       </c>
@@ -8948,7 +8872,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>False</t>
@@ -8984,15 +8907,15 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
         <v>3</v>
       </c>
@@ -9041,7 +8964,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>False</t>
@@ -9077,15 +8999,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -9135,7 +9057,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>False</t>
@@ -9171,15 +9092,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -9228,7 +9149,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
           <t>False</t>
@@ -9264,15 +9184,15 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9321,7 +9241,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
           <t>False</t>
@@ -9357,15 +9276,15 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -9414,7 +9333,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
           <t>False</t>
@@ -9450,15 +9368,15 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9507,7 +9425,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R97" t="inlineStr"/>
       <c r="S97" t="inlineStr">
         <is>
           <t>False</t>
@@ -9543,15 +9460,15 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
         <v>3</v>
       </c>
@@ -9600,7 +9517,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr"/>
       <c r="S98" t="inlineStr">
         <is>
           <t>True</t>
@@ -9636,15 +9552,15 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
         <v>3</v>
       </c>
@@ -9693,7 +9609,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R99" t="inlineStr"/>
       <c r="S99" t="inlineStr">
         <is>
           <t>False</t>
@@ -9729,15 +9644,15 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
         <v>3</v>
       </c>
@@ -9786,7 +9701,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr"/>
       <c r="S100" t="inlineStr">
         <is>
           <t>False</t>
@@ -9822,15 +9736,15 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9879,7 +9793,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R101" t="inlineStr"/>
       <c r="S101" t="inlineStr">
         <is>
           <t>False</t>
@@ -9915,15 +9828,15 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器（眼解剖）</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
+          <t>視覚機能の基礎と検査機器</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>生体と検査機器</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9972,7 +9885,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R102" t="inlineStr"/>
       <c r="S102" t="inlineStr">
         <is>
           <t>False</t>
@@ -10008,15 +9920,15 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -10065,7 +9977,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr"/>
       <c r="S103" t="inlineStr">
         <is>
           <t>False</t>
@@ -10101,15 +10012,15 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
         <v>2</v>
       </c>
@@ -10158,7 +10069,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr"/>
       <c r="S104" t="inlineStr">
         <is>
           <t>False</t>
@@ -10194,15 +10104,15 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>眼科検査学</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
+          <t>視能検査学</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>視能検査</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>3</v>
       </c>
@@ -10292,15 +10202,15 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10349,7 +10259,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr">
         <is>
           <t>True</t>
@@ -10385,15 +10294,15 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="n">
         <v>2</v>
       </c>
@@ -10442,7 +10351,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr">
         <is>
           <t>False</t>
@@ -10478,15 +10386,15 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="n">
         <v>2</v>
       </c>
@@ -10535,7 +10443,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R108" t="inlineStr"/>
       <c r="S108" t="inlineStr">
         <is>
           <t>False</t>
@@ -10571,15 +10478,15 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10628,7 +10535,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R109" t="inlineStr"/>
       <c r="S109" t="inlineStr">
         <is>
           <t>False</t>
@@ -10664,15 +10570,15 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="n">
         <v>2</v>
       </c>
@@ -10721,7 +10627,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr"/>
       <c r="S110" t="inlineStr">
         <is>
           <t>False</t>
@@ -10757,15 +10662,15 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>2</v>
       </c>
@@ -10814,7 +10719,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R111" t="inlineStr"/>
       <c r="S111" t="inlineStr">
         <is>
           <t>False</t>
@@ -10850,15 +10754,15 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>2</v>
       </c>
@@ -10907,7 +10811,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R112" t="inlineStr"/>
       <c r="S112" t="inlineStr">
         <is>
           <t>False</t>
@@ -10943,15 +10846,15 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -11000,7 +10903,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R113" t="inlineStr"/>
       <c r="S113" t="inlineStr">
         <is>
           <t>True</t>
@@ -11036,15 +10938,15 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>視覚生理学の基礎</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="n">
         <v>3</v>
       </c>
@@ -11093,7 +10995,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R114" t="inlineStr"/>
       <c r="S114" t="inlineStr">
         <is>
           <t>True</t>
@@ -11129,15 +11030,15 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="n">
         <v>3</v>
       </c>
@@ -11186,7 +11087,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R115" t="inlineStr"/>
       <c r="S115" t="inlineStr">
         <is>
           <t>False</t>
@@ -11222,15 +11122,15 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11279,7 +11179,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R116" t="inlineStr"/>
       <c r="S116" t="inlineStr">
         <is>
           <t>False</t>
@@ -11315,15 +11214,15 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11372,7 +11271,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr"/>
       <c r="S117" t="inlineStr">
         <is>
           <t>False</t>
@@ -11408,15 +11306,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -11465,7 +11363,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr">
         <is>
           <t>True</t>
@@ -11501,15 +11398,15 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11558,7 +11455,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr">
         <is>
           <t>False</t>
@@ -11594,15 +11490,15 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11651,7 +11547,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R120" t="inlineStr"/>
       <c r="S120" t="inlineStr">
         <is>
           <t>False</t>
@@ -11687,15 +11582,15 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11744,7 +11639,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr"/>
       <c r="S121" t="inlineStr">
         <is>
           <t>False</t>
@@ -11780,15 +11674,15 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="n">
         <v>3</v>
       </c>
@@ -11837,7 +11731,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr">
         <is>
           <t>False</t>
@@ -11873,15 +11766,15 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11930,7 +11823,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr">
         <is>
           <t>False</t>
@@ -11966,15 +11858,15 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="n">
         <v>1</v>
       </c>
@@ -12023,7 +11915,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr"/>
       <c r="S124" t="inlineStr">
         <is>
           <t>False</t>
@@ -12059,15 +11950,15 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -12116,7 +12007,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R125" t="inlineStr"/>
       <c r="S125" t="inlineStr">
         <is>
           <t>False</t>
@@ -12152,15 +12042,15 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>3</v>
       </c>
@@ -12209,7 +12099,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr">
         <is>
           <t>False</t>
@@ -12245,15 +12134,15 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
         <is>
           <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>2</v>
       </c>
@@ -12302,7 +12191,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr">
         <is>
           <t>False</t>
@@ -12338,15 +12226,15 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="n">
         <v>2</v>
       </c>
@@ -12395,7 +12283,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr"/>
       <c r="S128" t="inlineStr">
         <is>
           <t>False</t>
@@ -12431,15 +12318,15 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>弱視</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
         <is>
           <t>弱視の基本的知識</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>2</v>
       </c>
@@ -12488,7 +12375,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr"/>
       <c r="S129" t="inlineStr">
         <is>
           <t>False</t>
@@ -12524,15 +12410,15 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>斜視【斜視治療】</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
         <is>
           <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -12581,7 +12467,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R130" t="inlineStr"/>
       <c r="S130" t="inlineStr">
         <is>
           <t>True</t>
@@ -12617,15 +12502,15 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="n">
         <v>2</v>
       </c>
@@ -12715,15 +12600,15 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
           <t>両眼視機能と眼球運動</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>両眼視機能と眼球運動</t>
-        </is>
-      </c>
+      <c r="G132" t="inlineStr"/>
       <c r="H132" t="n">
         <v>4</v>
       </c>
@@ -12813,15 +12698,15 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -12870,7 +12755,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
       <c r="S133" t="inlineStr">
         <is>
           <t>True</t>
@@ -12906,15 +12790,15 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>2</v>
       </c>
@@ -12963,7 +12847,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
       <c r="S134" t="inlineStr">
         <is>
           <t>False</t>
@@ -12999,15 +12882,15 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="n">
         <v>5</v>
       </c>
@@ -13057,7 +12940,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
       <c r="S135" t="inlineStr">
         <is>
           <t>False</t>
@@ -13093,15 +12975,15 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13150,7 +13032,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
       <c r="S136" t="inlineStr">
         <is>
           <t>False</t>
@@ -13186,15 +13067,15 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>3</v>
       </c>
@@ -13243,7 +13124,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
       <c r="S137" t="inlineStr">
         <is>
           <t>False</t>
@@ -13279,15 +13159,15 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13336,7 +13216,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr">
         <is>
           <t>False</t>
@@ -13372,15 +13251,15 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>2</v>
       </c>
@@ -13429,7 +13308,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr">
         <is>
           <t>False</t>
@@ -13465,15 +13343,15 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>4</v>
       </c>
@@ -13522,7 +13400,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
       <c r="S140" t="inlineStr">
         <is>
           <t>False</t>
@@ -13558,15 +13435,15 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>斜視【各型】</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="n">
         <v>3</v>
       </c>
@@ -13615,7 +13492,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
       <c r="S141" t="inlineStr">
         <is>
           <t>True</t>
@@ -13654,12 +13530,12 @@
           <t>疾病と障害の成り立ち及び回復過程の促進</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
+      <c r="F142" t="inlineStr">
         <is>
           <t>病態の基礎</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="n">
         <v>3</v>
       </c>
@@ -13749,15 +13625,15 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13847,15 +13723,15 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13905,7 +13781,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr"/>
       <c r="S144" t="inlineStr">
         <is>
           <t>False</t>
@@ -13941,15 +13816,15 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -14039,15 +13914,15 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>2</v>
       </c>
@@ -14137,15 +14012,15 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>3</v>
       </c>
@@ -14235,15 +14110,15 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>眼疾病学</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
+          <t>視能障害学</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr"/>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14336,12 +14211,12 @@
           <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>視能訓練士の役割と義務</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>1</v>
       </c>
@@ -14391,7 +14266,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr"/>
       <c r="S149" t="inlineStr">
         <is>
           <t>False</t>
@@ -14427,15 +14301,15 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>生理光学</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
+          <t>基礎視能矯正学</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14485,7 +14359,6 @@
           <t>False</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr"/>
       <c r="S150" t="inlineStr">
         <is>
           <t>False</t>
@@ -14521,15 +14394,15 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>斜視【斜視検査】</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
+          <t>視能訓練学</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
         <is>
           <t>斜視の基本的知識</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="n">
         <v>4</v>
       </c>

--- a/CO国試data/CO_questions_2021.xlsx
+++ b/CO国試data/CO_questions_2021.xlsx
@@ -542,12 +542,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>薬物の副作用</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -818,12 +818,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>健康の指標</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -910,12 +910,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>公衆衛生学</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>公衆衛生学</t>
+          <t>公衆衛生総論</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>中枢神経の構造と機能</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>脳・神経</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>脳・神経</t>
+          <t>神経の構造と機能</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>病因と疾病の種類</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>内分泌</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>内分泌</t>
+          <t>内分泌器官の構造と機能</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の理念</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1830,12 +1830,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2014,12 +2014,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2204,12 +2204,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2400,12 +2400,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2492,12 +2492,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の展開</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2584,12 +2584,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2774,12 +2774,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -2866,12 +2866,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -2958,12 +2958,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3050,12 +3050,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3142,12 +3142,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視力検査</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正の枠組み</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>視能矯正の枠組み</t>
+          <t>視能矯正の展開</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3511,12 +3511,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>屈折検査</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3603,12 +3603,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>視野検査</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3885,12 +3885,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4069,12 +4069,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -4161,12 +4161,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4346,12 +4346,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4444,12 +4444,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>ぶどう膜</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -4720,12 +4720,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>涙器</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼窩</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>ぶどう膜</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5088,12 +5088,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>緑内障</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5180,12 +5180,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5272,12 +5272,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G53" t="inlineStr"/>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -5456,12 +5456,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -5824,12 +5824,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G59" t="inlineStr"/>
@@ -5916,12 +5916,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
@@ -6008,12 +6008,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の対象となる視能障害</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>視能矯正訓練の対象となる視能障害</t>
+          <t>機能的視能障害</t>
         </is>
       </c>
       <c r="G62" t="inlineStr"/>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -6376,12 +6376,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -6468,12 +6468,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -6560,12 +6560,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -6751,12 +6751,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -6849,12 +6849,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -6942,12 +6942,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -7040,12 +7040,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -7138,12 +7138,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G73" t="inlineStr"/>
@@ -7236,12 +7236,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>定義</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
@@ -7334,12 +7334,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
@@ -7428,12 +7428,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G76" t="inlineStr"/>
@@ -7521,12 +7521,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>保健、医療、福祉、介護の推進</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>保健、医療、福祉、介護の推進</t>
+          <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -7613,12 +7613,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -7705,12 +7705,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>遺伝</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>遺伝</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="G79" t="inlineStr"/>
@@ -7797,12 +7797,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>眼薬理学</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>眼薬理学</t>
+          <t>視能検査および視能矯正に用</t>
         </is>
       </c>
       <c r="G80" t="inlineStr"/>
@@ -7889,12 +7889,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>健康、疾病、障害の概念</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>健康、疾病、障害の概念</t>
+          <t>健康、疾病、障害の基本的知識</t>
         </is>
       </c>
       <c r="G81" t="inlineStr"/>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G82" t="inlineStr"/>
@@ -8073,12 +8073,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G83" t="inlineStr"/>
@@ -8165,12 +8165,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>人体の構造と機能及び心身の発達</t>
+          <t>遺伝</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>遺伝</t>
+          <t>遺伝子</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -8257,12 +8257,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G85" t="inlineStr"/>
@@ -8349,12 +8349,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G86" t="inlineStr"/>
@@ -8441,12 +8441,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G87" t="inlineStr"/>
@@ -8539,12 +8539,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G88" t="inlineStr"/>
@@ -8631,12 +8631,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G89" t="inlineStr"/>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G90" t="inlineStr"/>
@@ -8815,12 +8815,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼球運動</t>
         </is>
       </c>
       <c r="G91" t="inlineStr"/>
@@ -8907,12 +8907,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G92" t="inlineStr"/>
@@ -8999,12 +8999,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G93" t="inlineStr"/>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
@@ -9184,12 +9184,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G95" t="inlineStr"/>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼圧検査</t>
         </is>
       </c>
       <c r="G96" t="inlineStr"/>
@@ -9368,12 +9368,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G97" t="inlineStr"/>
@@ -9460,12 +9460,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G98" t="inlineStr"/>
@@ -9552,12 +9552,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G99" t="inlineStr"/>
@@ -9644,12 +9644,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G100" t="inlineStr"/>
@@ -9736,12 +9736,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>涙液検査</t>
         </is>
       </c>
       <c r="G101" t="inlineStr"/>
@@ -9828,12 +9828,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>視覚機能の基礎と検査機器</t>
+          <t>生体と検査機器</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>生体と検査機器</t>
+          <t>視能検査機器の基本的知識</t>
         </is>
       </c>
       <c r="G102" t="inlineStr"/>
@@ -9920,12 +9920,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>隅角検査</t>
         </is>
       </c>
       <c r="G103" t="inlineStr"/>
@@ -10012,12 +10012,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>硝子体</t>
         </is>
       </c>
       <c r="G104" t="inlineStr"/>
@@ -10104,12 +10104,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>視能検査学</t>
+          <t>視能検査</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>視能検査</t>
+          <t>眼底検査</t>
         </is>
       </c>
       <c r="G105" t="inlineStr"/>
@@ -10202,12 +10202,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G106" t="inlineStr"/>
@@ -10294,12 +10294,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G107" t="inlineStr"/>
@@ -10386,12 +10386,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G108" t="inlineStr"/>
@@ -10478,12 +10478,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G109" t="inlineStr"/>
@@ -10570,12 +10570,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G110" t="inlineStr"/>
@@ -10662,12 +10662,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G111" t="inlineStr"/>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G112" t="inlineStr"/>
@@ -10846,12 +10846,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G113" t="inlineStr"/>
@@ -10938,12 +10938,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と視覚生理学の基礎</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>視能矯正と視覚生理学の基礎</t>
+          <t>視覚生理学の基礎知識</t>
         </is>
       </c>
       <c r="G114" t="inlineStr"/>
@@ -11030,12 +11030,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>瞳孔</t>
         </is>
       </c>
       <c r="G115" t="inlineStr"/>
@@ -11122,12 +11122,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G116" t="inlineStr"/>
@@ -11214,12 +11214,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>水晶体</t>
         </is>
       </c>
       <c r="G117" t="inlineStr"/>
@@ -11306,12 +11306,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼外傷</t>
         </is>
       </c>
       <c r="G118" t="inlineStr"/>
@@ -11398,12 +11398,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G119" t="inlineStr"/>
@@ -11490,12 +11490,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G120" t="inlineStr"/>
@@ -11582,12 +11582,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G121" t="inlineStr"/>
@@ -11674,12 +11674,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>強膜</t>
         </is>
       </c>
       <c r="G122" t="inlineStr"/>
@@ -11766,12 +11766,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G123" t="inlineStr"/>
@@ -11858,12 +11858,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>網膜</t>
         </is>
       </c>
       <c r="G124" t="inlineStr"/>
@@ -11950,12 +11950,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G125" t="inlineStr"/>
@@ -12042,12 +12042,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G126" t="inlineStr"/>
@@ -12134,12 +12134,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の基本的知識</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>視能矯正訓練の基本的知識</t>
+          <t>観血的視能矯正</t>
         </is>
       </c>
       <c r="G127" t="inlineStr"/>
@@ -12226,12 +12226,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
@@ -12318,12 +12318,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>弱視の基本的知識</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>弱視の基本的知識</t>
+          <t>病因論</t>
         </is>
       </c>
       <c r="G129" t="inlineStr"/>
@@ -12410,12 +12410,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>視能矯正訓練の知識と技術</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>視能矯正訓練の知識と技術</t>
+          <t>弱視訓練</t>
         </is>
       </c>
       <c r="G130" t="inlineStr"/>
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>生理光学の基礎知識</t>
         </is>
       </c>
       <c r="G131" t="inlineStr"/>
@@ -12600,12 +12600,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>両眼視機能と眼球運動</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>両眼視機能と眼球運動</t>
+          <t>両眼視</t>
         </is>
       </c>
       <c r="G132" t="inlineStr"/>
@@ -12698,12 +12698,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の異常</t>
         </is>
       </c>
       <c r="G133" t="inlineStr"/>
@@ -12790,12 +12790,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G134" t="inlineStr"/>
@@ -12882,12 +12882,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G135" t="inlineStr"/>
@@ -12975,12 +12975,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G136" t="inlineStr"/>
@@ -13067,12 +13067,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G137" t="inlineStr"/>
@@ -13159,12 +13159,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
@@ -13251,12 +13251,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G139" t="inlineStr"/>
@@ -13343,12 +13343,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G140" t="inlineStr"/>
@@ -13435,12 +13435,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G141" t="inlineStr"/>
@@ -13527,12 +13527,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>疾病と障害の成り立ち及び回復過程の促進</t>
+          <t>病態の基礎</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>病態の基礎</t>
+          <t>病因と疾病の種類</t>
         </is>
       </c>
       <c r="G142" t="inlineStr"/>
@@ -13625,12 +13625,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -13723,12 +13723,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -13816,12 +13816,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -13914,12 +13914,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -14012,12 +14012,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>視神経、視路</t>
         </is>
       </c>
       <c r="G147" t="inlineStr"/>
@@ -14110,12 +14110,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>視能障害学</t>
+          <t>主要眼疾患の基本的知識</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>主要眼疾患の基本的知識</t>
+          <t>眼瞼</t>
         </is>
       </c>
       <c r="G148" t="inlineStr"/>
@@ -14208,12 +14208,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>保健医療福祉と視能障害のリハビリテーションの理念</t>
+          <t>視能訓練士の役割と義務</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>視能訓練士の役割と義務</t>
+          <t>医療の質と安全の確保</t>
         </is>
       </c>
       <c r="G149" t="inlineStr"/>
@@ -14301,12 +14301,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>基礎視能矯正学</t>
+          <t>視能矯正と生理光学の基礎</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>視能矯正と生理光学の基礎</t>
+          <t>屈折、調節の矯正</t>
         </is>
       </c>
       <c r="G150" t="inlineStr"/>
@@ -14394,12 +14394,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>視能訓練学</t>
+          <t>斜視の基本的知識</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>斜視の基本的知識</t>
+          <t>分類</t>
         </is>
       </c>
       <c r="G151" t="inlineStr"/>

--- a/CO国試data/CO_questions_2021.xlsx
+++ b/CO国試data/CO_questions_2021.xlsx
@@ -550,7 +550,11 @@
           <t>薬物の副作用</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>中毒、ショック</t>
+        </is>
+      </c>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -642,7 +646,6 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -734,7 +737,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -826,7 +833,11 @@
           <t>健康の指標</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>人口問題</t>
+        </is>
+      </c>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -918,7 +929,6 @@
           <t>公衆衛生総論</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1010,7 +1020,6 @@
           <t>中枢神経の構造と機能</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1102,7 +1111,11 @@
           <t>神経の構造と機能</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>神経細胞、神経線維、軸索、髄鞘、神経膠細胞</t>
+        </is>
+      </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -1194,7 +1207,6 @@
           <t>病因と疾病の種類</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -1286,7 +1298,11 @@
           <t>内分泌器官の構造と機能</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>下垂体</t>
+        </is>
+      </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
@@ -1378,7 +1394,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>1</v>
       </c>
@@ -1470,7 +1485,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H12" t="n">
         <v>3</v>
       </c>
@@ -1562,7 +1581,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>近見反応</t>
+        </is>
+      </c>
       <c r="H13" t="n">
         <v>3</v>
       </c>
@@ -1654,7 +1677,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>3</v>
       </c>
@@ -1746,7 +1768,6 @@
           <t>視能矯正の理念</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1</v>
       </c>
@@ -1838,7 +1859,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>4</v>
       </c>
@@ -1930,7 +1950,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>両眼共同運動、両眼離反運動</t>
+        </is>
+      </c>
       <c r="H17" t="n">
         <v>3</v>
       </c>
@@ -2022,7 +2046,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>共同筋と拮抗筋</t>
+        </is>
+      </c>
       <c r="H18" t="n">
         <v>1</v>
       </c>
@@ -2114,7 +2142,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>4</v>
       </c>
@@ -2212,7 +2239,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H20" t="n">
         <v>3</v>
       </c>
@@ -2310,7 +2341,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H21" t="n">
         <v>3</v>
       </c>
@@ -2408,7 +2443,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H22" t="n">
         <v>2</v>
       </c>
@@ -2500,7 +2539,11 @@
           <t>視能矯正の展開</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>視能訓練士の業務と管理、運営</t>
+        </is>
+      </c>
       <c r="H23" t="n">
         <v>1</v>
       </c>
@@ -2592,7 +2635,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>3</v>
       </c>
@@ -2684,7 +2726,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H25" t="n">
         <v>4</v>
       </c>
@@ -2782,7 +2828,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H26" t="n">
         <v>3</v>
       </c>
@@ -2874,7 +2924,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>遠視</t>
+        </is>
+      </c>
       <c r="H27" t="n">
         <v>3</v>
       </c>
@@ -2966,7 +3020,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H28" t="n">
         <v>3</v>
       </c>
@@ -3058,7 +3116,11 @@
           <t>外眼筋の作用と眼球運動</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>外眼筋の単独作用</t>
+        </is>
+      </c>
       <c r="H29" t="n">
         <v>4</v>
       </c>
@@ -3150,7 +3212,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>2</v>
       </c>
@@ -3242,7 +3303,6 @@
           <t>視力検査</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>2</v>
       </c>
@@ -3334,7 +3394,6 @@
           <t>視能矯正の展開</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>2</v>
       </c>
@@ -3426,7 +3485,6 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>4</v>
       </c>
@@ -3519,7 +3577,11 @@
           <t>屈折検査</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>他覚的屈折検査（波面収差解析を含む）</t>
+        </is>
+      </c>
       <c r="H34" t="n">
         <v>2</v>
       </c>
@@ -3611,7 +3673,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
         <v>3</v>
       </c>
@@ -3709,7 +3770,11 @@
           <t>視野検査</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>動的、静的視野測定法（自動視野計を含む）</t>
+        </is>
+      </c>
       <c r="H36" t="n">
         <v>3</v>
       </c>
@@ -3801,7 +3866,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
         <v>3</v>
       </c>
@@ -3893,7 +3957,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H38" t="n">
         <v>3</v>
       </c>
@@ -3985,7 +4053,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H39" t="n">
         <v>2</v>
       </c>
@@ -4077,7 +4149,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>2</v>
       </c>
@@ -4169,7 +4240,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H41" t="n">
         <v>4</v>
       </c>
@@ -4262,7 +4337,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H42" t="n">
         <v>1</v>
       </c>
@@ -4354,7 +4433,6 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
         <v>3</v>
       </c>
@@ -4452,7 +4530,6 @@
           <t>ぶどう膜</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>2</v>
       </c>
@@ -4544,7 +4621,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H45" t="n">
         <v>3</v>
       </c>
@@ -4636,7 +4717,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H46" t="n">
         <v>3</v>
       </c>
@@ -4728,7 +4813,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
         <v>2</v>
       </c>
@@ -4820,7 +4904,11 @@
           <t>涙器</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>涙液分泌減少症、眼乾燥症〈ドライアイ〉</t>
+        </is>
+      </c>
       <c r="H48" t="n">
         <v>2</v>
       </c>
@@ -4912,7 +5000,11 @@
           <t>眼窩</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>眼窩吹き抜け骨折</t>
+        </is>
+      </c>
       <c r="H49" t="n">
         <v>2</v>
       </c>
@@ -5004,7 +5096,11 @@
           <t>ぶどう膜</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ぶどう膜炎</t>
+        </is>
+      </c>
       <c r="H50" t="n">
         <v>2</v>
       </c>
@@ -5096,7 +5192,11 @@
           <t>緑内障</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>正常眼圧緑内障</t>
+        </is>
+      </c>
       <c r="H51" t="n">
         <v>2</v>
       </c>
@@ -5188,7 +5288,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H52" t="n">
         <v>3</v>
       </c>
@@ -5280,7 +5384,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>形態覚遮断弱視</t>
+        </is>
+      </c>
       <c r="H53" t="n">
         <v>3</v>
       </c>
@@ -5372,7 +5480,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>不同視弱視</t>
+        </is>
+      </c>
       <c r="H54" t="n">
         <v>3</v>
       </c>
@@ -5464,7 +5576,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>斜視特殊型</t>
+        </is>
+      </c>
       <c r="H55" t="n">
         <v>3</v>
       </c>
@@ -5556,7 +5672,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H56" t="n">
         <v>3</v>
       </c>
@@ -5648,7 +5768,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>屈折矯正</t>
+        </is>
+      </c>
       <c r="H57" t="n">
         <v>4</v>
       </c>
@@ -5740,7 +5864,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
         <v>3</v>
       </c>
@@ -5832,7 +5955,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H59" t="n">
         <v>3</v>
       </c>
@@ -5924,7 +6051,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H60" t="n">
         <v>2</v>
       </c>
@@ -6016,7 +6147,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H61" t="n">
         <v>3</v>
       </c>
@@ -6108,7 +6243,6 @@
           <t>機能的視能障害</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
         <v>3</v>
       </c>
@@ -6200,7 +6334,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
         <v>4</v>
       </c>
@@ -6292,7 +6425,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>点眼薬</t>
+        </is>
+      </c>
       <c r="H64" t="n">
         <v>2</v>
       </c>
@@ -6384,7 +6521,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H65" t="n">
         <v>3</v>
       </c>
@@ -6476,7 +6617,11 @@
           <t>輻湊、開散と屈折、調節</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>測定法</t>
+        </is>
+      </c>
       <c r="H66" t="n">
         <v>3</v>
       </c>
@@ -6568,7 +6713,6 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
         <v>4</v>
       </c>
@@ -6666,7 +6810,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H68" t="n">
         <v>3</v>
       </c>
@@ -6759,7 +6907,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
         <v>4</v>
       </c>
@@ -6857,7 +7004,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H70" t="n">
         <v>4</v>
       </c>
@@ -6950,7 +7101,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
         <v>4</v>
       </c>
@@ -7048,7 +7198,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
         <v>3</v>
       </c>
@@ -7146,7 +7295,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>視交叉から後頭葉までの視覚伝導路の疾患</t>
+        </is>
+      </c>
       <c r="H73" t="n">
         <v>4</v>
       </c>
@@ -7244,7 +7397,6 @@
           <t>定義</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
         <v>3</v>
       </c>
@@ -7342,7 +7494,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>プリズム</t>
+        </is>
+      </c>
       <c r="H75" t="n">
         <v>5</v>
       </c>
@@ -7436,7 +7592,6 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
         <v>4</v>
       </c>
@@ -7529,7 +7684,6 @@
           <t>保健、医療、福祉、介護制度</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
         <v>2</v>
       </c>
@@ -7621,7 +7775,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>副交感神経薬</t>
+        </is>
+      </c>
       <c r="H78" t="n">
         <v>2</v>
       </c>
@@ -7713,7 +7871,11 @@
           <t>遺伝子</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>染色体</t>
+        </is>
+      </c>
       <c r="H79" t="n">
         <v>1</v>
       </c>
@@ -7805,7 +7967,11 @@
           <t>視能検査および視能矯正に用</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>点眼薬</t>
+        </is>
+      </c>
       <c r="H80" t="n">
         <v>2</v>
       </c>
@@ -7897,7 +8063,6 @@
           <t>健康、疾病、障害の基本的知識</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
         <v>2</v>
       </c>
@@ -7989,7 +8154,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
         <v>2</v>
       </c>
@@ -8081,7 +8245,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
         <v>3</v>
       </c>
@@ -8173,7 +8336,11 @@
           <t>遺伝子</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>基本構造と機能</t>
+        </is>
+      </c>
       <c r="H84" t="n">
         <v>3</v>
       </c>
@@ -8265,7 +8432,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
         <v>2</v>
       </c>
@@ -8357,7 +8523,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
         <v>1</v>
       </c>
@@ -8449,7 +8614,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
         <v>3</v>
       </c>
@@ -8547,7 +8711,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
         <v>3</v>
       </c>
@@ -8639,7 +8802,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H89" t="n">
         <v>3</v>
       </c>
@@ -8731,7 +8898,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
         <v>2</v>
       </c>
@@ -8823,7 +8989,11 @@
           <t>眼球運動</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>神経筋接合部障害</t>
+        </is>
+      </c>
       <c r="H91" t="n">
         <v>3</v>
       </c>
@@ -8915,7 +9085,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H92" t="n">
         <v>3</v>
       </c>
@@ -9007,7 +9181,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>結像と収差</t>
+        </is>
+      </c>
       <c r="H93" t="n">
         <v>2</v>
       </c>
@@ -9100,7 +9278,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
         <v>2</v>
       </c>
@@ -9192,7 +9369,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>近視</t>
+        </is>
+      </c>
       <c r="H95" t="n">
         <v>3</v>
       </c>
@@ -9284,7 +9465,6 @@
           <t>眼圧検査</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
         <v>2</v>
       </c>
@@ -9376,7 +9556,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Schirmer試験</t>
+        </is>
+      </c>
       <c r="H97" t="n">
         <v>2</v>
       </c>
@@ -9468,7 +9652,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>生体染色検査</t>
+        </is>
+      </c>
       <c r="H98" t="n">
         <v>3</v>
       </c>
@@ -9560,7 +9748,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H99" t="n">
         <v>3</v>
       </c>
@@ -9652,7 +9844,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H100" t="n">
         <v>3</v>
       </c>
@@ -9744,7 +9940,11 @@
           <t>涙液検査</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>涙液層破壊時間〈BUT〉</t>
+        </is>
+      </c>
       <c r="H101" t="n">
         <v>2</v>
       </c>
@@ -9836,7 +10036,6 @@
           <t>視能検査機器の基本的知識</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
         <v>2</v>
       </c>
@@ -9928,7 +10127,6 @@
           <t>隅角検査</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
         <v>2</v>
       </c>
@@ -10020,7 +10218,11 @@
           <t>硝子体</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>硝子体出血、混濁、後部硝子体剥離</t>
+        </is>
+      </c>
       <c r="H104" t="n">
         <v>2</v>
       </c>
@@ -10112,7 +10314,6 @@
           <t>眼底検査</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
         <v>3</v>
       </c>
@@ -10210,7 +10411,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
         <v>3</v>
       </c>
@@ -10302,7 +10502,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H107" t="n">
         <v>2</v>
       </c>
@@ -10394,7 +10598,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>視覚の成り立ち</t>
+        </is>
+      </c>
       <c r="H108" t="n">
         <v>2</v>
       </c>
@@ -10486,7 +10694,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
       <c r="H109" t="n">
         <v>3</v>
       </c>
@@ -10578,7 +10785,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>外斜視</t>
+        </is>
+      </c>
       <c r="H110" t="n">
         <v>2</v>
       </c>
@@ -10670,7 +10881,6 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
         <v>2</v>
       </c>
@@ -10762,7 +10972,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
       <c r="H112" t="n">
         <v>2</v>
       </c>
@@ -10854,7 +11063,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>視覚生理学</t>
+        </is>
+      </c>
       <c r="H113" t="n">
         <v>2</v>
       </c>
@@ -10946,7 +11159,11 @@
           <t>視覚生理学の基礎知識</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>視覚の閾値</t>
+        </is>
+      </c>
       <c r="H114" t="n">
         <v>3</v>
       </c>
@@ -11038,7 +11255,11 @@
           <t>瞳孔</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>瞳孔不同</t>
+        </is>
+      </c>
       <c r="H115" t="n">
         <v>3</v>
       </c>
@@ -11130,7 +11351,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>老視</t>
+        </is>
+      </c>
       <c r="H116" t="n">
         <v>2</v>
       </c>
@@ -11222,7 +11447,11 @@
           <t>水晶体</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>白内障</t>
+        </is>
+      </c>
       <c r="H117" t="n">
         <v>2</v>
       </c>
@@ -11314,7 +11543,6 @@
           <t>眼外傷</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
       <c r="H118" t="n">
         <v>2</v>
       </c>
@@ -11406,7 +11634,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr"/>
       <c r="H119" t="n">
         <v>2</v>
       </c>
@@ -11498,7 +11725,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>網膜剥離</t>
+        </is>
+      </c>
       <c r="H120" t="n">
         <v>2</v>
       </c>
@@ -11590,7 +11821,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>網膜色素変性、その他の変性およびジストロフィ</t>
+        </is>
+      </c>
       <c r="H121" t="n">
         <v>2</v>
       </c>
@@ -11682,7 +11917,11 @@
           <t>強膜</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>強膜炎</t>
+        </is>
+      </c>
       <c r="H122" t="n">
         <v>3</v>
       </c>
@@ -11774,7 +12013,11 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>うっ血乳頭</t>
+        </is>
+      </c>
       <c r="H123" t="n">
         <v>2</v>
       </c>
@@ -11866,7 +12109,11 @@
           <t>網膜</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>糖尿病網膜症</t>
+        </is>
+      </c>
       <c r="H124" t="n">
         <v>1</v>
       </c>
@@ -11958,7 +12205,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>内斜視</t>
+        </is>
+      </c>
       <c r="H125" t="n">
         <v>3</v>
       </c>
@@ -12050,7 +12301,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
       <c r="H126" t="n">
         <v>3</v>
       </c>
@@ -12142,7 +12392,6 @@
           <t>観血的視能矯正</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
       <c r="H127" t="n">
         <v>2</v>
       </c>
@@ -12234,7 +12483,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>交代性上斜位</t>
+        </is>
+      </c>
       <c r="H128" t="n">
         <v>2</v>
       </c>
@@ -12326,7 +12579,6 @@
           <t>病因論</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" t="n">
         <v>2</v>
       </c>
@@ -12418,7 +12670,11 @@
           <t>弱視訓練</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>遮閉法</t>
+        </is>
+      </c>
       <c r="H130" t="n">
         <v>3</v>
       </c>
@@ -12510,7 +12766,11 @@
           <t>生理光学の基礎知識</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>レンズ</t>
+        </is>
+      </c>
       <c r="H131" t="n">
         <v>2</v>
       </c>
@@ -12608,7 +12868,11 @@
           <t>両眼視</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>網膜対応、両眼視野</t>
+        </is>
+      </c>
       <c r="H132" t="n">
         <v>4</v>
       </c>
@@ -12706,7 +12970,11 @@
           <t>屈折、調節の異常</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>乱視</t>
+        </is>
+      </c>
       <c r="H133" t="n">
         <v>3</v>
       </c>
@@ -12798,7 +13066,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
       <c r="H134" t="n">
         <v>2</v>
       </c>
@@ -12890,7 +13157,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H135" t="n">
         <v>5</v>
       </c>
@@ -12983,7 +13254,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
       <c r="H136" t="n">
         <v>3</v>
       </c>
@@ -13075,7 +13345,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
       <c r="H137" t="n">
         <v>3</v>
       </c>
@@ -13167,7 +13436,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
       <c r="H138" t="n">
         <v>3</v>
       </c>
@@ -13259,7 +13527,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
         <v>2</v>
       </c>
@@ -13351,7 +13618,6 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
       <c r="H140" t="n">
         <v>4</v>
       </c>
@@ -13443,7 +13709,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>回旋斜視</t>
+        </is>
+      </c>
       <c r="H141" t="n">
         <v>3</v>
       </c>
@@ -13535,7 +13805,11 @@
           <t>病因と疾病の種類</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>循環障害</t>
+        </is>
+      </c>
       <c r="H142" t="n">
         <v>3</v>
       </c>
@@ -13633,7 +13907,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
       <c r="H143" t="n">
         <v>4</v>
       </c>
@@ -13731,7 +14004,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>コンタクトレンズ</t>
+        </is>
+      </c>
       <c r="H144" t="n">
         <v>3</v>
       </c>
@@ -13824,7 +14101,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
       <c r="H145" t="n">
         <v>3</v>
       </c>
@@ -13922,7 +14198,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
       <c r="H146" t="n">
         <v>2</v>
       </c>
@@ -14020,7 +14295,6 @@
           <t>視神経、視路</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
       <c r="H147" t="n">
         <v>3</v>
       </c>
@@ -14118,7 +14392,11 @@
           <t>眼瞼</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>睫毛乱生</t>
+        </is>
+      </c>
       <c r="H148" t="n">
         <v>3</v>
       </c>
@@ -14216,7 +14494,6 @@
           <t>医療の質と安全の確保</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
       <c r="H149" t="n">
         <v>1</v>
       </c>
@@ -14309,7 +14586,11 @@
           <t>屈折、調節の矯正</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>眼鏡レンズ</t>
+        </is>
+      </c>
       <c r="H150" t="n">
         <v>3</v>
       </c>
@@ -14402,7 +14683,11 @@
           <t>分類</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>麻痺性斜視</t>
+        </is>
+      </c>
       <c r="H151" t="n">
         <v>4</v>
       </c>

--- a/CO国試data/CO_questions_2021.xlsx
+++ b/CO国試data/CO_questions_2021.xlsx
@@ -603,10 +603,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S2" t="b">
+        <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -694,10 +692,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S3" t="b">
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -790,10 +786,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S4" t="b">
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -886,10 +880,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S5" t="b">
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -977,10 +969,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S6" t="b">
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1068,10 +1058,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S7" t="b">
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1164,10 +1152,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S8" t="b">
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1255,10 +1241,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S9" t="b">
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1351,10 +1335,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S10" t="b">
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1442,10 +1424,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S11" t="b">
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1538,10 +1518,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S12" t="b">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1634,10 +1612,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S13" t="b">
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1725,10 +1701,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S14" t="b">
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1816,10 +1790,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S15" t="b">
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1907,10 +1879,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S16" t="b">
+        <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2003,10 +1973,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S17" t="b">
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2099,10 +2067,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S18" t="b">
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2196,10 +2162,8 @@
           <t>2021_co_21_am018.jpg</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S19" t="b">
+        <v>0</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2298,10 +2262,8 @@
           <t>2021_co_21_am019.jpg</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S20" t="b">
+        <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2400,10 +2362,8 @@
           <t>2021_co_21_am020.jpg</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S21" t="b">
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2496,10 +2456,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S22" t="b">
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2592,10 +2550,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S23" t="b">
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2785,10 +2741,8 @@
           <t>2021_co_21_am024.jpg</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S25" t="b">
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2881,10 +2835,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S26" t="b">
+        <v>0</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2977,10 +2929,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S27" t="b">
+        <v>0</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3260,10 +3210,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S30" t="b">
+        <v>0</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3351,10 +3299,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S31" t="b">
+        <v>0</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3442,10 +3388,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S32" t="b">
+        <v>0</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3534,10 +3478,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S33" t="b">
+        <v>0</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3630,10 +3572,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S34" t="b">
+        <v>0</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3727,10 +3667,8 @@
           <t>2021_co_21_am034.jpg</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S35" t="b">
+        <v>0</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3823,10 +3761,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S36" t="b">
+        <v>0</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3914,10 +3850,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S37" t="b">
+        <v>0</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4106,10 +4040,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S39" t="b">
+        <v>0</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4197,10 +4129,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S40" t="b">
+        <v>0</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4294,10 +4224,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S41" t="b">
+        <v>0</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4390,10 +4318,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S42" t="b">
+        <v>0</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4578,10 +4504,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S44" t="b">
+        <v>0</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4674,10 +4598,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S45" t="b">
+        <v>0</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4770,10 +4692,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S46" t="b">
+        <v>0</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -4861,10 +4781,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S47" t="b">
+        <v>0</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -4957,10 +4875,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S48" t="b">
+        <v>0</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5053,10 +4969,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S49" t="b">
+        <v>0</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5149,10 +5063,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S50" t="b">
+        <v>0</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5245,10 +5157,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S51" t="b">
+        <v>0</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5341,10 +5251,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S52" t="b">
+        <v>0</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5437,10 +5345,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S53" t="b">
+        <v>0</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5533,10 +5439,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S54" t="b">
+        <v>0</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5629,10 +5533,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S55" t="b">
+        <v>0</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5725,10 +5627,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S56" t="b">
+        <v>0</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -5821,10 +5721,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S57" t="b">
+        <v>0</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -5912,10 +5810,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S58" t="b">
+        <v>0</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6008,10 +5904,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S59" t="b">
+        <v>0</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6104,10 +5998,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S60" t="b">
+        <v>0</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6200,10 +6092,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S61" t="b">
+        <v>0</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6291,10 +6181,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S62" t="b">
+        <v>0</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6478,10 +6366,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S64" t="b">
+        <v>0</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6574,10 +6460,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S65" t="b">
+        <v>0</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6670,10 +6554,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S66" t="b">
+        <v>0</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -6767,10 +6649,8 @@
           <t>2021_co_21_am066.jpg</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S67" t="b">
+        <v>0</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -6864,10 +6744,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S68" t="b">
+        <v>0</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -6961,10 +6839,8 @@
           <t>2021_co_21_am068.jpg</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S69" t="b">
+        <v>0</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7058,10 +6934,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S70" t="b">
+        <v>0</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7252,10 +7126,8 @@
           <t>2021_co_21_am071.jpg</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S72" t="b">
+        <v>0</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7354,10 +7226,8 @@
           <t>2021_co_21_am072.jpg</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S73" t="b">
+        <v>0</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7451,10 +7321,8 @@
           <t>2021_co_21_am073.jpg</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S74" t="b">
+        <v>0</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7549,10 +7417,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S75" t="b">
+        <v>0</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -7641,10 +7507,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S76" t="b">
+        <v>0</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7732,10 +7596,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S77" t="b">
+        <v>0</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -7828,10 +7690,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S78" t="b">
+        <v>0</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -7924,10 +7784,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S79" t="b">
+        <v>0</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8020,10 +7878,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S80" t="b">
+        <v>0</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8111,10 +7967,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S81" t="b">
+        <v>0</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8202,10 +8056,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S82" t="b">
+        <v>0</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8293,10 +8145,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S83" t="b">
+        <v>0</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8480,10 +8330,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S85" t="b">
+        <v>0</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8571,10 +8419,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S86" t="b">
+        <v>0</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8668,10 +8514,8 @@
           <t>2021_co_21_pm011.jpg</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S87" t="b">
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -8855,10 +8699,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S89" t="b">
+        <v>0</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -8946,10 +8788,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S90" t="b">
+        <v>0</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9042,10 +8882,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S91" t="b">
+        <v>0</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9138,10 +8976,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S92" t="b">
+        <v>0</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9235,10 +9071,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S93" t="b">
+        <v>0</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9326,10 +9160,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S94" t="b">
+        <v>0</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9422,10 +9254,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S95" t="b">
+        <v>0</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9513,10 +9343,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S96" t="b">
+        <v>0</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -9609,10 +9437,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S97" t="b">
+        <v>0</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -9801,10 +9627,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S99" t="b">
+        <v>0</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -9897,10 +9721,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S100" t="b">
+        <v>0</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -9993,10 +9815,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S101" t="b">
+        <v>0</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10084,10 +9904,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S102" t="b">
+        <v>0</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10175,10 +9993,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S103" t="b">
+        <v>0</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10271,10 +10087,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S104" t="b">
+        <v>0</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10368,10 +10182,8 @@
           <t>2021_co_21_pm029.jpg</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S105" t="b">
+        <v>0</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10459,10 +10271,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S106" t="b">
+        <v>0</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10555,10 +10365,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S107" t="b">
+        <v>0</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -10651,10 +10459,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S108" t="b">
+        <v>0</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -10742,10 +10548,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S109" t="b">
+        <v>0</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -10838,10 +10642,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S110" t="b">
+        <v>0</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -10929,10 +10731,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S111" t="b">
+        <v>0</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -11020,10 +10820,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S112" t="b">
+        <v>0</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -11212,10 +11010,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S114" t="b">
+        <v>0</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -11308,10 +11104,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S115" t="b">
+        <v>0</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -11404,10 +11198,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S116" t="b">
+        <v>0</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -11500,10 +11292,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S117" t="b">
+        <v>0</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -11682,10 +11472,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S119" t="b">
+        <v>0</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -11778,10 +11566,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S120" t="b">
+        <v>0</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -11874,10 +11660,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S121" t="b">
+        <v>0</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -11970,10 +11754,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S122" t="b">
+        <v>0</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -12066,10 +11848,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S123" t="b">
+        <v>0</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -12162,10 +11942,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S124" t="b">
+        <v>0</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12258,10 +12036,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S125" t="b">
+        <v>0</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12349,10 +12125,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S126" t="b">
+        <v>0</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -12440,10 +12214,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S127" t="b">
+        <v>0</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12536,10 +12308,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S128" t="b">
+        <v>0</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -12627,10 +12397,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S129" t="b">
+        <v>0</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -12723,10 +12491,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S130" t="b">
+        <v>0</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -12825,10 +12591,8 @@
           <t>2021_co_21_pm055.jpg</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S131" t="b">
+        <v>0</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -12927,10 +12691,8 @@
           <t>2021_co_21_pm056.jpg</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S132" t="b">
+        <v>0</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -13114,10 +12876,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S134" t="b">
+        <v>0</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -13211,10 +12971,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S135" t="b">
+        <v>0</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -13302,10 +13060,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S136" t="b">
+        <v>0</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -13393,10 +13149,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S137" t="b">
+        <v>0</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -13484,10 +13238,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S138" t="b">
+        <v>0</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -13575,10 +13327,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S139" t="b">
+        <v>0</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -13666,10 +13416,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S140" t="b">
+        <v>0</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -13864,10 +13612,8 @@
           <t>2021_co_21_pm066.jpg</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S142" t="b">
+        <v>0</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -13961,10 +13707,8 @@
           <t>2021_co_21_pm067.jpg</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S143" t="b">
+        <v>0</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -14058,10 +13802,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S144" t="b">
+        <v>0</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -14155,10 +13897,8 @@
           <t>2021_co_21_pm069.jpg</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S145" t="b">
+        <v>0</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -14252,10 +13992,8 @@
           <t>2021_co_21_pm070.jpg</t>
         </is>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S146" t="b">
+        <v>0</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -14349,10 +14087,8 @@
           <t>2021_co_21_pm071.jpg</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S147" t="b">
+        <v>0</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -14451,10 +14187,8 @@
           <t>2021_co_21_pm072.jpg</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S148" t="b">
+        <v>0</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -14543,10 +14277,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S149" t="b">
+        <v>0</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -14640,10 +14372,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S150" t="b">
+        <v>0</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -14742,10 +14472,8 @@
           <t>2021_co_21_pm075.jpg</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
+      <c r="S151" t="b">
+        <v>0</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>

--- a/CO国試data/CO_questions_2021.xlsx
+++ b/CO国試data/CO_questions_2021.xlsx
@@ -2626,7 +2626,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2639,10 +2639,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S24" t="b">
+        <v>1</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2822,7 +2820,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>ABCDE</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2836,7 +2834,7 @@
         </is>
       </c>
       <c r="S26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3010,7 +3008,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3023,10 +3021,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S28" t="b">
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3106,7 +3102,7 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3119,10 +3115,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S29" t="b">
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3931,7 +3925,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3944,10 +3938,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S38" t="b">
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4395,7 +4387,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4413,10 +4405,8 @@
           <t>2021_co_21_am042.jpg</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S43" t="b">
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -6257,7 +6247,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CD</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6270,10 +6260,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S63" t="b">
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7011,7 +6999,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7029,10 +7017,8 @@
           <t>2021_co_21_am070.jpg</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S71" t="b">
+        <v>1</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8226,7 +8212,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -8239,10 +8225,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S84" t="b">
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8590,7 +8574,7 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BC</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -8603,10 +8587,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S88" t="b">
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9518,7 +9500,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -9531,10 +9513,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S98" t="b">
+        <v>1</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10901,7 +10881,7 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -10914,10 +10894,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S113" t="b">
+        <v>1</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -11368,7 +11346,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -11381,10 +11359,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S118" t="b">
+        <v>1</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -12772,7 +12748,7 @@
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -12785,10 +12761,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S133" t="b">
+        <v>1</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -13497,7 +13471,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -13510,10 +13484,8 @@
           <t>False</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
+      <c r="S141" t="b">
+        <v>1</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
